--- a/datapackages/sisor/data/BASE_REPASSE_RECURSOS.xlsx
+++ b/datapackages/sisor/data/BASE_REPASSE_RECURSOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,35 +1785,35 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1271</v>
+        <v>2011</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4491</v>
+        <v>1941</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>130003000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="43">
@@ -1826,11 +1826,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1941</v>
+        <v>1501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1846,16 +1846,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>150000</v>
+        <v>6311890</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2011</v>
+        <v>1011</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1879,31 +1879,31 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6311890</v>
+        <v>104706</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1011</v>
+        <v>4111</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1501</v>
+        <v>1915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -1912,39 +1912,6 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>104706</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>4111</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1915</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F46" t="n">
-        <v>61</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
         <v>98000</v>
       </c>
     </row>
